--- a/data/trans_orig/IP3107-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3107-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20665</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40924</t>
+          <t>41615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24061</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28397</t>
+          <t>29002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35102</t>
+          <t>33892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61293</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>42990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>63270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88784</t>
+          <t>89409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117941</t>
+          <t>117679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50922</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134780</t>
+          <t>133608</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158066</t>
+          <t>158316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133318</t>
+          <t>133191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156188</t>
+          <t>156309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273952</t>
+          <t>273159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307015</t>
+          <t>305709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18915</t>
+          <t>18928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>34968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28780</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85442</t>
+          <t>86208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101076</t>
+          <t>101334</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89896</t>
+          <t>91217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107108</t>
+          <t>106822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180219</t>
+          <t>180837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204096</t>
+          <t>203978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>28076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>42293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>155865</t>
+          <t>154758</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170265</t>
+          <t>169688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>157283</t>
+          <t>156991</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>175138</t>
+          <t>175122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317635</t>
+          <t>318011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>341181</t>
+          <t>341884</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>79134</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106757</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87700</t>
+          <t>88405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>117374</t>
+          <t>117344</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>176059</t>
+          <t>176062</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>217683</t>
+          <t>218551</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24484</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48210</t>
+          <t>47935</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51740</t>
+          <t>53540</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>65198</t>
+          <t>64425</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>91809</t>
+          <t>91791</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29934</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>403712</t>
+          <t>403989</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>438196</t>
+          <t>440301</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>414669</t>
+          <t>413917</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>450237</t>
+          <t>450797</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>831372</t>
+          <t>831745</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>879904</t>
+          <t>882105</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29876</t>
+          <t>29826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>32678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48563</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>28697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>27925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37105</t>
+          <t>36764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53347</t>
+          <t>53892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42191</t>
+          <t>43475</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17452</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>15877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31492</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23939</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42212</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37283</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59147</t>
+          <t>59252</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26282</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>40503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154840</t>
+          <t>153952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175589</t>
+          <t>174530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160032</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185346</t>
+          <t>184595</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320628</t>
+          <t>320946</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353268</t>
+          <t>354301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,82 +5979,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10919</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6229</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17135</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>25650</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>18163</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>34518</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,02%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>10919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6293</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17159</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>25650</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>18969</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>33995</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110683</t>
+          <t>109984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127663</t>
+          <t>127467</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119349</t>
+          <t>119590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135316</t>
+          <t>135194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234711</t>
+          <t>234899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258164</t>
+          <t>257981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29611</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145547</t>
+          <t>144722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>158506</t>
+          <t>158651</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>129875</t>
+          <t>129661</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148009</t>
+          <t>147975</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>281690</t>
+          <t>281022</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>303862</t>
+          <t>302624</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>36836</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57548</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>83277</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113915</t>
+          <t>112578</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27347</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31670</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>54585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,77 +7343,77 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>61246</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>50708</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>75125</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>100539</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>86176</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>117875</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>61246</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>49793</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>74688</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>100539</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>85162</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48065</t>
+          <t>49539</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>53079</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77622</t>
+          <t>78887</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>443985</t>
+          <t>443536</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>477341</t>
+          <t>476741</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>444075</t>
+          <t>444648</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>479606</t>
+          <t>480679</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>898583</t>
+          <t>897740</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>947008</t>
+          <t>947279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26036</t>
+          <t>26335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44338</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>44797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>41171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63392</t>
+          <t>64632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81924</t>
+          <t>83399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>24753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,47 +9087,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>36600</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>27847</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>46869</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>10,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>36600</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>28199</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>47605</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166876</t>
+          <t>167046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182270</t>
+          <t>183004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200026</t>
+          <t>200348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219522</t>
+          <t>220645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370565</t>
+          <t>371844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396195</t>
+          <t>397334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30596</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142908</t>
+          <t>141591</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159952</t>
+          <t>159762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>152949</t>
+          <t>152884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>168513</t>
+          <t>169347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>300356</t>
+          <t>301025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>323652</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>543</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146036</t>
+          <t>145728</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>159149</t>
+          <t>159394</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>139224</t>
+          <t>140102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154210</t>
+          <t>154703</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>290266</t>
+          <t>290388</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>311297</t>
+          <t>309720</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46291</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26202</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59543</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86109</t>
+          <t>86789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>28237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70650</t>
+          <t>71106</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>61835</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30133</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52594</t>
+          <t>51116</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77207</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>106558</t>
+          <t>107081</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>501825</t>
+          <t>501461</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>533015</t>
+          <t>532190</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>537648</t>
+          <t>538165</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>571964</t>
+          <t>571222</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1048934</t>
+          <t>1045306</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1094573</t>
+          <t>1092909</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
